--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="To Send" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sent Log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="To Send" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sent Log" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -57,9 +60,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,8 +433,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -472,7 +480,1354 @@
           <t>Mrs Example</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>wakhidirazane@gmail.com</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Razane</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CV@Arabianfal.com</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Cv@aldawaa.com.sa</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hr.qrm@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rec@alojami.com</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Recruitment@rawabiholding.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Job.s6@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Careers@dnata.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Hr@alesayi_motors.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Hr@alrayan.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Recruiting.ksa@mcmcermott.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Recruitment@aytb.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wadaef@gtecorp.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Careers@nesr.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Recruit@farm.com.sa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Info@alhumamlaw.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hr1@gulfteksaudi.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Catcosa@catcosa.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cv@tafear.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Recruitment@sraco.com.sa</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Info@atco.com.sa</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HRdepartmental@sa.yokogawa.com</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Recruitment@shadeco.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Klc.hr@alkafaa.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Kbr-amcdehr@kbr.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Recruitment@batook.com</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Career@shawarmer.com</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hrsupport@archirodon.net</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jobs@binajinah.com</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Marketing.np@nesma.com</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wadaef2019@abdulla-fouad.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Careers@innosoft.sa</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M@startime.com.sa</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>job@musk.sa.com</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Shababwatansa@gmail.com</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>j@sabksa.com</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>al.alshaikh@bonyan.sa</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ymohammed@innovest.com.sa</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>s.alwadi@nhc.sa</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>i.atassi@artar.com.sa</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>oalkhunaizi@darwaemaar.com</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>jobs@almasah.net</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>recruitment.amjad@gmail.com</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>jobrydlaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Job@almoosahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>recruitment@almoosahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>jobs@sghgroup.net</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>career.dmm@sghgroup.net</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>talent.acquisition@drsulaimanalhabib.com</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Careers@jhah.com</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>hrd@alahsahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>career@almanahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>info@familycare.com.sa</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>info@ramclinics.com</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>HR.DSFHR@fakeeh.care</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>career@mouwasat.com</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>careers@dallah-hospital.com</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>hr.phc@drsulaimanalhabib.com</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>careers@almurjanhospital.com</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>hiringnow.ksa@gmail.com</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Career@sidco.com.sa</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>recruitment@wecareksa.com</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>jobs@impact.sa</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>careers@alascon.com.sa</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>jobs@sabkaljusore.com</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>hr-recruitment@areebhr.com</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>info@batterjeepharma.com</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>jobs.hr@ezdhar-ksa.com</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Careers@abdullahaljassar.com</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>hr@whitespacesa.com</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>hiring@rayafinancing.com</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>recruitment@ueg-ksa.com</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>HR@masheerde.sa</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Rec@one1.sa</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Hr@alshrouqexpress.com</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Recruitment@Aknans.com</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>bnoon.hr@bnoon.sa</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ksajobs@arabou.edu.sa</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>recruitment@ouqoud.sa</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Hiring Manager</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Draft created - press Send in Gmail</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -485,8 +1840,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -540,6 +1895,3328 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>46324.51496594907</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>wakhidirazane@gmail.com</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Dear Razane,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>46324.57030294561</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CV@Arabianfal.com</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>46324.57055829509</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Cv@aldawaa.com.sa</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>46324.57082257781</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Hr.qrm@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>46324.57107523186</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rec@alojami.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>46324.57132873026</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Recruitment@rawabiholding.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>46324.57158374105</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Job.s6@hotmail.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>46324.57184151871</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Careers@dnata.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>46324.57209786151</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Hr@alesayi_motors.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>46324.57235266713</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hr@alrayan.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>46324.57260750505</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Recruiting.ksa@mcmcermott.com</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>46324.57286822861</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Recruitment@aytb.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>46324.57314793847</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Wadaef@gtecorp.com</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>46324.57340038744</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Careers@nesr.com</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46324.57365402101</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Recruit@farm.com.sa</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46324.57390884</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Info@alhumamlaw.com</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46324.57417986276</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Hr1@gulfteksaudi.com</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46324.57443507319</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Catcosa@catcosa.com</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46324.57469346</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Cv@tafear.com</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46324.57495894685</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Recruitment@sraco.com.sa</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46324.57521969776</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Info@atco.com.sa</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>46324.57547133757</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HRdepartmental@sa.yokogawa.com</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>46324.5757232595</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Recruitment@shadeco.com</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>46324.57597448669</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Klc.hr@alkafaa.com</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>46324.57622710484</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Kbr-amcdehr@kbr.com</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>46324.57650208128</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Recruitment@batook.com</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>46324.57675357427</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Career@shawarmer.com</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>46324.5770057825</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Hrsupport@archirodon.net</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>46324.57725823795</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jobs@binajinah.com</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>46324.57751246596</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Marketing.np@nesma.com</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>46324.57777210544</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Wadaef2019@abdulla-fouad.com</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>46324.57803719492</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Careers@innosoft.sa</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>46324.5782917478</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>M@startime.com.sa</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>46324.57854583382</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>job@musk.sa.com</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>46324.57879785298</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Shababwatansa@gmail.com</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>46324.57905149531</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>j@sabksa.com</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>46324.57930277257</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>al.alshaikh@bonyan.sa</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>46324.57955870283</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ymohammed@innovest.com.sa</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>46324.57982117712</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>s.alwadi@nhc.sa</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>46324.59040165185</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>i.atassi@artar.com.sa</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>46324.59065644182</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>oalkhunaizi@darwaemaar.com</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>46324.59090773377</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>jobs@almasah.net</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>46324.59116096496</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>recruitment.amjad@gmail.com</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>46324.59141472193</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>jobrydlaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>46324.59169591335</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Job@almoosahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46324.59195022025</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>recruitment@almoosahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>46324.59222098844</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>jobs@sghgroup.net</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46324.59256647354</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>career.dmm@sghgroup.net</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46324.59283410751</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>talent.acquisition@drsulaimanalhabib.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>46324.59314905736</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Careers@jhah.com</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46324.59341120975</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>hrd@alahsahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46324.59367570325</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>career@almanahospital.com.sa</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46324.59393895346</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>info@familycare.com.sa</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46324.59419248231</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>info@ramclinics.com</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46324.59446028361</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>HR.DSFHR@fakeeh.care</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46324.59471573559</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>career@mouwasat.com</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46324.59498045648</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>careers@dallah-hospital.com</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46324.5952317778</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>hr.phc@drsulaimanalhabib.com</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46324.59548336967</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>careers@almurjanhospital.com</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46324.59574268464</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>hiringnow.ksa@gmail.com</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46324.59599750482</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Career@sidco.com.sa</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46324.59625289205</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>recruitment@wecareksa.com</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46324.59650718937</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>jobs@impact.sa</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46324.59677615655</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>careers@alascon.com.sa</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46324.59703391369</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>jobs@sabkaljusore.com</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46324.5972930344</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>hr-recruitment@areebhr.com</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46324.59755170347</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>info@batterjeepharma.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46324.59781084086</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>jobs.hr@ezdhar-ksa.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46324.59807404546</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Careers@abdullahaljassar.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46324.59832877114</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>hr@whitespacesa.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46324.59859670626</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>hiring@rayafinancing.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46324.59885087841</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>recruitment@ueg-ksa.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46324.59910508966</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HR@masheerde.sa</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46324.59935725669</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Rec@one1.sa</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46324.59961049656</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Hr@alshrouqexpress.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>46324.59987010455</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Recruitment@Aknans.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>46324.60012810244</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>bnoon.hr@bnoon.sa</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>46324.60038273261</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ksajobs@arabou.edu.sa</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>46324.60064537214</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>October 2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>recruitment@ouqoud.sa</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Spontaneous Application – Full Stack Developer | Razane Wakhidi</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Dear Hiring Manager,
+My name is Razane Wakhidi, and I am a Full Stack Developer reaching out to express my interest in potential job opportunities within your company.
+I have hands-on experience in web development, working with technologies such as PHP, Laravel, JavaScript, Node.js, and databases to build and maintain web applications.
+Trained in Agile/Scrum methodologies, I am adaptable, proactive, and eager to learn new technologies based on project requirements. I enjoy solving technical challenges, taking initiative, and contributing to meaningful projects.
+I am currently seeking an opportunity to join a professional development team where I can contribute my technical skills, gain valuable experience, and grow as a Full Stack Developer.
+I am open to relocation and would be happy to discuss on-site, hybrid, or remote opportunities depending on your company's needs.
+Please find my CV attached for your consideration. I would be grateful if you could consider my profile for any current or future opportunities that match my skills.
+Thank you for your time and consideration. I look forward to the possibility of hearing from you.
+Best regards,
+Razane Wakhidi
+Full Stack Developer
+Phone: +212 6 45 39 73 30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
